--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -21992,6 +21992,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B941" t="n">
+        <v>0</v>
+      </c>
+      <c r="C941" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D941" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E941" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="F941" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="G941" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B942" t="n">
+        <v>2667</v>
+      </c>
+      <c r="C942" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="D942" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="E942" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="F942" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="G942" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22038,6 +22038,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="943">
+      <c r="A943" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B943" t="n">
+        <v>1381</v>
+      </c>
+      <c r="C943" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D943" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="E943" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F943" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G943" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22061,6 +22061,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B944" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C944" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="D944" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E944" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F944" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="G944" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22084,6 +22084,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="945">
+      <c r="A945" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B945" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C945" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="D945" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E945" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="F945" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G945" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -21925,22 +21925,22 @@
     </row>
     <row r="938">
       <c r="A938" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B938" t="n">
-        <v>1120</v>
+        <v>100</v>
       </c>
       <c r="C938" t="n">
-        <v>9.30000019073486</v>
+        <v>9.19999980926514</v>
       </c>
       <c r="D938" t="n">
-        <v>9</v>
+        <v>9.19999980926514</v>
       </c>
       <c r="E938" t="n">
         <v>9.19999980926514</v>
       </c>
       <c r="F938" t="n">
-        <v>9.30000019073486</v>
+        <v>9.19999980926514</v>
       </c>
       <c r="G938" t="s">
         <v>7</v>
@@ -21948,19 +21948,19 @@
     </row>
     <row r="939">
       <c r="A939" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B939" t="n">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="C939" t="n">
         <v>9.30000019073486</v>
       </c>
       <c r="D939" t="n">
-        <v>9.30000019073486</v>
+        <v>9</v>
       </c>
       <c r="E939" t="n">
-        <v>9.30000019073486</v>
+        <v>9.19999980926514</v>
       </c>
       <c r="F939" t="n">
         <v>9.30000019073486</v>
@@ -21971,22 +21971,22 @@
     </row>
     <row r="940">
       <c r="A940" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B940" t="n">
-        <v>1670</v>
+        <v>0</v>
       </c>
       <c r="C940" t="n">
         <v>9.30000019073486</v>
       </c>
       <c r="D940" t="n">
-        <v>9.25</v>
+        <v>9.30000019073486</v>
       </c>
       <c r="E940" t="n">
         <v>9.30000019073486</v>
       </c>
       <c r="F940" t="n">
-        <v>9.25</v>
+        <v>9.30000019073486</v>
       </c>
       <c r="G940" t="s">
         <v>7</v>
@@ -21994,19 +21994,19 @@
     </row>
     <row r="941">
       <c r="A941" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B941" t="n">
-        <v>0</v>
+        <v>1670</v>
       </c>
       <c r="C941" t="n">
-        <v>9.25</v>
+        <v>9.30000019073486</v>
       </c>
       <c r="D941" t="n">
         <v>9.25</v>
       </c>
       <c r="E941" t="n">
-        <v>9.25</v>
+        <v>9.30000019073486</v>
       </c>
       <c r="F941" t="n">
         <v>9.25</v>
@@ -22017,22 +22017,22 @@
     </row>
     <row r="942">
       <c r="A942" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B942" t="n">
-        <v>2667</v>
+        <v>0</v>
       </c>
       <c r="C942" t="n">
-        <v>9.39999961853027</v>
+        <v>9.25</v>
       </c>
       <c r="D942" t="n">
-        <v>8.85000038146973</v>
+        <v>9.25</v>
       </c>
       <c r="E942" t="n">
-        <v>8.85000038146973</v>
+        <v>9.25</v>
       </c>
       <c r="F942" t="n">
-        <v>9.39999961853027</v>
+        <v>9.25</v>
       </c>
       <c r="G942" t="s">
         <v>7</v>
@@ -22040,22 +22040,22 @@
     </row>
     <row r="943">
       <c r="A943" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B943" t="n">
-        <v>1381</v>
+        <v>2667</v>
       </c>
       <c r="C943" t="n">
-        <v>9.5</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="D943" t="n">
-        <v>9.05000019073486</v>
+        <v>8.85000038146973</v>
       </c>
       <c r="E943" t="n">
-        <v>9.5</v>
+        <v>8.85000038146973</v>
       </c>
       <c r="F943" t="n">
-        <v>9.5</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="G943" t="s">
         <v>7</v>
@@ -22063,22 +22063,22 @@
     </row>
     <row r="944">
       <c r="A944" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B944" t="n">
-        <v>2400</v>
+        <v>1381</v>
       </c>
       <c r="C944" t="n">
-        <v>9.69999980926514</v>
+        <v>9.5</v>
       </c>
       <c r="D944" t="n">
-        <v>9.44999980926514</v>
+        <v>9.05000019073486</v>
       </c>
       <c r="E944" t="n">
         <v>9.5</v>
       </c>
       <c r="F944" t="n">
-        <v>9.69999980926514</v>
+        <v>9.5</v>
       </c>
       <c r="G944" t="s">
         <v>7</v>
@@ -22086,22 +22086,22 @@
     </row>
     <row r="945">
       <c r="A945" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B945" t="n">
-        <v>1950</v>
+        <v>2400</v>
       </c>
       <c r="C945" t="n">
         <v>9.69999980926514</v>
       </c>
       <c r="D945" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E945" t="n">
         <v>9.5</v>
       </c>
-      <c r="E945" t="n">
+      <c r="F945" t="n">
         <v>9.69999980926514</v>
-      </c>
-      <c r="F945" t="n">
-        <v>9.5</v>
       </c>
       <c r="G945" t="s">
         <v>7</v>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -25023,6 +25023,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B949" t="n">
+        <v>4318</v>
+      </c>
+      <c r="C949" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D949" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E949" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="F949" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="G949" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="H949" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -25049,6 +25049,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B950" t="n">
+        <v>177</v>
+      </c>
+      <c r="C950" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D950" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E950" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="F950" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="G950" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H950" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -25075,6 +25075,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B951" t="n">
+        <v>20</v>
+      </c>
+      <c r="C951" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="D951" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E951" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F951" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="G951" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="H951" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -25101,6 +25101,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B952" t="n">
+        <v>2442</v>
+      </c>
+      <c r="C952" t="n">
+        <v>9</v>
+      </c>
+      <c r="D952" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="E952" t="n">
+        <v>9</v>
+      </c>
+      <c r="F952" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="G952" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="H952" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -25179,6 +25179,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B955" t="n">
+        <v>11945</v>
+      </c>
+      <c r="C955" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D955" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="E955" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="F955" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="G955" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="H955" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22399,8 +22399,31 @@
       <c r="E958" t="n">
         <v>9.35000038146973</v>
       </c>
-      <c r="F958"/>
+      <c r="F958" t="n">
+        <v>9.35000038146973</v>
+      </c>
       <c r="G958" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B959" t="n">
+        <v>1834</v>
+      </c>
+      <c r="C959" t="n">
+        <v>9.85000038146973</v>
+      </c>
+      <c r="D959" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E959" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="F959"/>
+      <c r="G959" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22422,8 +22422,31 @@
       <c r="E959" t="n">
         <v>9.44999980926514</v>
       </c>
-      <c r="F959"/>
+      <c r="F959" t="n">
+        <v>9.75</v>
+      </c>
       <c r="G959" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B960" t="n">
+        <v>380</v>
+      </c>
+      <c r="C960" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="D960" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="E960" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="F960"/>
+      <c r="G960" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22445,8 +22445,31 @@
       <c r="E960" t="n">
         <v>9.39999961853027</v>
       </c>
-      <c r="F960"/>
+      <c r="F960" t="n">
+        <v>9.30000019073486</v>
+      </c>
       <c r="G960" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B961" t="n">
+        <v>600</v>
+      </c>
+      <c r="C961" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="D961" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="E961" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="F961"/>
+      <c r="G961" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22468,8 +22468,31 @@
       <c r="E961" t="n">
         <v>9.35000038146973</v>
       </c>
-      <c r="F961"/>
+      <c r="F961" t="n">
+        <v>9.35000038146973</v>
+      </c>
       <c r="G961" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B962" t="n">
+        <v>17</v>
+      </c>
+      <c r="C962" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="D962" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="E962" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="F962"/>
+      <c r="G962" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -22498,6 +22498,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B963" t="n">
+        <v>77</v>
+      </c>
+      <c r="C963" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="D963" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="E963" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="F963" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="G963" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -25465,6 +25465,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B966" t="n">
+        <v>506</v>
+      </c>
+      <c r="C966" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="D966" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E966" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F966" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="G966" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="H966" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -25491,6 +25491,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B967" t="n">
+        <v>263</v>
+      </c>
+      <c r="C967" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="D967" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E967" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F967" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="G967" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="H967" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28421,6 +28421,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" t="s">
+        <v>9</v>
+      </c>
+      <c r="B968" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C968" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="D968" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E968" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F968" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G968" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H968" t="n">
+        <v>860</v>
+      </c>
+      <c r="I968" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28450,6 +28450,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" t="s">
+        <v>9</v>
+      </c>
+      <c r="B969" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C969" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D969" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E969" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F969" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G969" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H969" t="n">
+        <v>0</v>
+      </c>
+      <c r="I969" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28479,6 +28479,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" t="s">
+        <v>9</v>
+      </c>
+      <c r="B970" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C970" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D970" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E970" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F970" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G970" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H970" t="n">
+        <v>0</v>
+      </c>
+      <c r="I970" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28508,6 +28508,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="s">
+        <v>9</v>
+      </c>
+      <c r="B971" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C971" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D971" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E971" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F971" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G971" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H971" t="n">
+        <v>0</v>
+      </c>
+      <c r="I971" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="s">
+        <v>9</v>
+      </c>
+      <c r="B972" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C972" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D972" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="E972" t="n">
+        <v>9.14999961853027</v>
+      </c>
+      <c r="F972" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="G972" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="H972" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I972" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28566,6 +28566,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="s">
+        <v>9</v>
+      </c>
+      <c r="B973" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C973" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="D973" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E973" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="F973" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G973" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H973" t="n">
+        <v>360</v>
+      </c>
+      <c r="I973" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28595,6 +28595,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="974">
+      <c r="A974" t="s">
+        <v>9</v>
+      </c>
+      <c r="B974" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C974" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D974" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E974" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F974" t="n">
+        <v>8.94999980926514</v>
+      </c>
+      <c r="G974" t="n">
+        <v>8.94999980926514</v>
+      </c>
+      <c r="H974" t="n">
+        <v>25010</v>
+      </c>
+      <c r="I974" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28624,6 +28624,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" t="s">
+        <v>9</v>
+      </c>
+      <c r="B975" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C975" t="n">
+        <v>9</v>
+      </c>
+      <c r="D975" t="n">
+        <v>9</v>
+      </c>
+      <c r="E975" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="F975" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="G975" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="H975" t="n">
+        <v>1735</v>
+      </c>
+      <c r="I975" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28653,6 +28653,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="976">
+      <c r="A976" t="s">
+        <v>9</v>
+      </c>
+      <c r="B976" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C976" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D976" t="n">
+        <v>9</v>
+      </c>
+      <c r="E976" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F976" t="n">
+        <v>9</v>
+      </c>
+      <c r="G976" t="n">
+        <v>9</v>
+      </c>
+      <c r="H976" t="n">
+        <v>465</v>
+      </c>
+      <c r="I976" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MGS.MI.xlsx
+++ b/data/MGS.MI.xlsx
@@ -28682,6 +28682,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" t="s">
+        <v>9</v>
+      </c>
+      <c r="B977" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C977" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D977" t="n">
+        <v>8.94999980926514</v>
+      </c>
+      <c r="E977" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F977" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="G977" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="H977" t="n">
+        <v>2995</v>
+      </c>
+      <c r="I977" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
